--- a/docs/pension_data_combined_2026-10-01.xlsx
+++ b/docs/pension_data_combined_2026-10-01.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1761</v>
-      </c>
       <c r="D48" t="n">
         <v>4249014.3</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-10-01</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.1785</v>
       </c>
       <c r="D55" t="n">
         <v>57123758.69</v>

--- a/docs/pension_data_combined_2026-10-01.xlsx
+++ b/docs/pension_data_combined_2026-10-01.xlsx
@@ -1224,6 +1224,9 @@
           <t>2026-10-01</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>1.1761</v>
+      </c>
       <c r="D48" t="n">
         <v>4249014.3</v>
       </c>
@@ -1346,6 +1349,9 @@
         <is>
           <t>2026-10-01</t>
         </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1.1785</v>
       </c>
       <c r="D55" t="n">
         <v>57123758.69</v>
